--- a/BOM DevBoard.xlsx
+++ b/BOM DevBoard.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27928"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30430"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\mkuipers\Documents\KiCAD\TUP4041\TUP-devboard\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\MeinK\Documents\KiCad\TUP4041\TUP-devboard\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3B379AFE-45F7-4A47-ABC4-66F20BA31EE2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8658B035-31CC-4A6E-9641-1C8A0F8244C1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-30660" yWindow="-885" windowWidth="22725" windowHeight="16545" xr2:uid="{FCFF9A81-ACBB-439F-8FFF-0C5ABBE65E83}"/>
+    <workbookView xWindow="-29595" yWindow="3495" windowWidth="27735" windowHeight="16260" xr2:uid="{FCFF9A81-ACBB-439F-8FFF-0C5ABBE65E83}"/>
   </bookViews>
   <sheets>
     <sheet name="Blad1" sheetId="1" r:id="rId1"/>
@@ -44,7 +44,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="127" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="144" uniqueCount="108">
   <si>
     <t>TULIP4041 DevBoard BOM</t>
   </si>
@@ -55,9 +55,6 @@
     <t>Qty</t>
   </si>
   <si>
-    <t>Pinstrip socket 20 pin</t>
-  </si>
-  <si>
     <t>Pico analyzer hookup</t>
   </si>
   <si>
@@ -79,27 +76,15 @@
     <t>Pico plugin</t>
   </si>
   <si>
-    <t>Pinstrip male 20 pin</t>
-  </si>
-  <si>
-    <t>Pinstrip male 12 pin</t>
-  </si>
-  <si>
     <t>HP41 analyzer hookup</t>
   </si>
   <si>
-    <t>Pinstrip male 2 pin</t>
-  </si>
-  <si>
     <t>IR LED current limiter</t>
   </si>
   <si>
     <t>IR led</t>
   </si>
   <si>
-    <t>flatcable with 2* header female</t>
-  </si>
-  <si>
     <t>114-00841-68, AMP SD card connector</t>
   </si>
   <si>
@@ -208,9 +193,6 @@
     <t>HP41 module connector</t>
   </si>
   <si>
-    <t>Resistor 270R 5% / 1/4W</t>
-  </si>
-  <si>
     <t>Resistor 1M 5% / 1/4W</t>
   </si>
   <si>
@@ -232,9 +214,6 @@
     <t>not needed if you do not plan to hookup an analyzer or scope</t>
   </si>
   <si>
-    <t>Jumper 2.54mm</t>
-  </si>
-  <si>
     <t>jumper pins</t>
   </si>
   <si>
@@ -259,9 +238,6 @@
     <t>jumper, 2-pin header with jumper</t>
   </si>
   <si>
-    <t>Pinstrip male 6 pin</t>
-  </si>
-  <si>
     <t>max length 15-20 cm, optional, or build your own or use jumper cables</t>
   </si>
   <si>
@@ -292,9 +268,6 @@
     <t>when closed allows driving PWO (JP1 must be open in this case)</t>
   </si>
   <si>
-    <t>when closed enables driving the IR led (IR is not supported in the BETA software) JP3 must be open in this case!</t>
-  </si>
-  <si>
     <t>when closed allows powering the TULIP DevBoard from the HP41 when no USB power is present</t>
   </si>
   <si>
@@ -320,6 +293,81 @@
   </si>
   <si>
     <t>Pico2 headers</t>
+  </si>
+  <si>
+    <t>Pinstrip male 20 pin, 2.54mm</t>
+  </si>
+  <si>
+    <t>Pinstrip socket 20 pin, 2.54mm</t>
+  </si>
+  <si>
+    <t>Pinstrip male 12 pin, 2.54mm</t>
+  </si>
+  <si>
+    <t>Pinstrip male 2 pin, 2.54mm</t>
+  </si>
+  <si>
+    <t>Jumper, 2.54mm</t>
+  </si>
+  <si>
+    <t>Pinstrip male 6 pin, 2.54mm</t>
+  </si>
+  <si>
+    <t>flatcable with 2* header female,, 2.54mm</t>
+  </si>
+  <si>
+    <t>when closed enables driving the IR led, JP3 must be open in this case!</t>
+  </si>
+  <si>
+    <t>Reference</t>
+  </si>
+  <si>
+    <t>J2, J3</t>
+  </si>
+  <si>
+    <t>U1</t>
+  </si>
+  <si>
+    <t>J5</t>
+  </si>
+  <si>
+    <t>JP1, JP2, JP3, JP4</t>
+  </si>
+  <si>
+    <t>J4</t>
+  </si>
+  <si>
+    <t>Resistor 200k 5% / 1/4W</t>
+  </si>
+  <si>
+    <t>R1</t>
+  </si>
+  <si>
+    <t>R6</t>
+  </si>
+  <si>
+    <t>R2,3,4,5,7,8</t>
+  </si>
+  <si>
+    <t>D1</t>
+  </si>
+  <si>
+    <t>Q1</t>
+  </si>
+  <si>
+    <t>U4</t>
+  </si>
+  <si>
+    <t>J1</t>
+  </si>
+  <si>
+    <t>U3</t>
+  </si>
+  <si>
+    <t>U2, U5</t>
+  </si>
+  <si>
+    <t>Resistor 200R 5% / 1/4W</t>
   </si>
 </sst>
 </file>
@@ -724,426 +772,478 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EBC0D742-A60C-4E2F-903E-5FA4DD69759C}">
-  <dimension ref="A1:J32"/>
+  <dimension ref="A1:K31"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="28.85546875" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="28.5703125" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="25.42578125" customWidth="1"/>
     <col min="6" max="6" width="19.42578125" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="31.140625" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="20.140625" customWidth="1"/>
+    <col min="8" max="8" width="15.5703125" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="31.140625" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="20.140625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" s="2" customFormat="1" ht="18.75" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:10" s="2" customFormat="1" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="2" spans="1:9" s="1" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:10" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B2" s="1" t="s">
         <v>1</v>
       </c>
       <c r="C2" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="D2" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="D2" s="1" t="s">
+      <c r="E2" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="E2" s="1" t="s">
+      <c r="F2" s="1" t="s">
         <v>7</v>
-      </c>
-      <c r="F2" s="1" t="s">
-        <v>8</v>
       </c>
       <c r="G2" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="H2" s="1" t="s">
-        <v>9</v>
+      <c r="H2" s="3" t="s">
+        <v>91</v>
       </c>
       <c r="I2" s="1" t="s">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="3" spans="1:9" x14ac:dyDescent="0.25">
+        <v>8</v>
+      </c>
+      <c r="J2" s="1" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="3" spans="1:10" x14ac:dyDescent="0.25">
       <c r="B3" t="s">
-        <v>11</v>
+        <v>83</v>
       </c>
       <c r="E3" t="s">
-        <v>46</v>
+        <v>41</v>
       </c>
       <c r="G3">
         <v>2</v>
       </c>
       <c r="H3" t="s">
-        <v>4</v>
+        <v>92</v>
       </c>
       <c r="I3" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="4" spans="1:9" x14ac:dyDescent="0.25">
+        <v>3</v>
+      </c>
+      <c r="J3" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="4" spans="1:10" x14ac:dyDescent="0.25">
       <c r="B4" t="s">
-        <v>3</v>
+        <v>84</v>
       </c>
       <c r="C4" t="s">
-        <v>27</v>
+        <v>22</v>
       </c>
       <c r="D4" s="4" t="s">
-        <v>64</v>
+        <v>57</v>
       </c>
       <c r="E4" t="s">
-        <v>65</v>
+        <v>58</v>
       </c>
       <c r="F4" s="5" t="s">
-        <v>66</v>
+        <v>59</v>
       </c>
       <c r="G4" s="5">
         <v>2</v>
       </c>
-      <c r="H4" t="s">
-        <v>10</v>
+      <c r="H4" s="5" t="s">
+        <v>93</v>
       </c>
       <c r="I4" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="5" spans="1:9" x14ac:dyDescent="0.25">
+        <v>9</v>
+      </c>
+      <c r="J4" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="5" spans="1:10" x14ac:dyDescent="0.25">
       <c r="B5" t="s">
-        <v>12</v>
+        <v>85</v>
       </c>
       <c r="E5" t="s">
-        <v>46</v>
+        <v>41</v>
       </c>
       <c r="G5">
         <v>1</v>
       </c>
       <c r="H5" t="s">
-        <v>13</v>
+        <v>94</v>
       </c>
       <c r="I5" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="6" spans="1:9" x14ac:dyDescent="0.25">
+        <v>10</v>
+      </c>
+      <c r="J5" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="6" spans="1:10" x14ac:dyDescent="0.25">
       <c r="B6" t="s">
-        <v>14</v>
+        <v>86</v>
       </c>
       <c r="E6" t="s">
-        <v>46</v>
+        <v>41</v>
       </c>
       <c r="G6">
         <v>4</v>
       </c>
       <c r="H6" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="7" spans="1:9" x14ac:dyDescent="0.25">
+        <v>95</v>
+      </c>
+      <c r="I6" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="7" spans="1:10" x14ac:dyDescent="0.25">
       <c r="B7" t="s">
-        <v>62</v>
+        <v>87</v>
       </c>
       <c r="E7" t="s">
-        <v>46</v>
+        <v>41</v>
       </c>
       <c r="G7">
         <v>4</v>
       </c>
       <c r="H7" t="s">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="8" spans="1:9" x14ac:dyDescent="0.25">
+        <v>95</v>
+      </c>
+      <c r="I7" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="8" spans="1:10" x14ac:dyDescent="0.25">
       <c r="B8" t="s">
-        <v>71</v>
+        <v>88</v>
       </c>
       <c r="E8" t="s">
-        <v>46</v>
+        <v>41</v>
       </c>
       <c r="G8">
         <v>2</v>
       </c>
       <c r="H8" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="9" spans="1:9" x14ac:dyDescent="0.25">
+        <v>96</v>
+      </c>
+      <c r="I8" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="9" spans="1:10" x14ac:dyDescent="0.25">
       <c r="B9" t="s">
-        <v>17</v>
+        <v>89</v>
       </c>
       <c r="C9" t="s">
-        <v>27</v>
+        <v>22</v>
       </c>
       <c r="D9" s="4" t="s">
+        <v>54</v>
+      </c>
+      <c r="E9" t="s">
         <v>60</v>
-      </c>
-      <c r="E9" t="s">
-        <v>67</v>
       </c>
       <c r="G9">
         <v>1</v>
       </c>
-      <c r="H9" t="s">
-        <v>45</v>
-      </c>
       <c r="I9" t="s">
-        <v>72</v>
-      </c>
-    </row>
-    <row r="10" spans="1:9" x14ac:dyDescent="0.25">
+        <v>40</v>
+      </c>
+      <c r="J9" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="10" spans="1:10" x14ac:dyDescent="0.25">
       <c r="B10" t="s">
-        <v>54</v>
+        <v>107</v>
       </c>
       <c r="E10" t="s">
-        <v>46</v>
+        <v>41</v>
       </c>
       <c r="G10">
         <v>1</v>
       </c>
       <c r="H10" t="s">
-        <v>15</v>
+        <v>98</v>
       </c>
       <c r="I10" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="11" spans="1:9" x14ac:dyDescent="0.25">
+        <v>11</v>
+      </c>
+      <c r="J10" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="11" spans="1:10" x14ac:dyDescent="0.25">
       <c r="B11" t="s">
-        <v>54</v>
+        <v>97</v>
       </c>
       <c r="E11" t="s">
-        <v>46</v>
+        <v>41</v>
       </c>
       <c r="G11">
         <v>1</v>
       </c>
       <c r="H11" t="s">
+        <v>99</v>
+      </c>
+      <c r="I11" t="s">
+        <v>44</v>
+      </c>
+      <c r="J11" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="12" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="B12" t="s">
         <v>49</v>
       </c>
-      <c r="I11" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="12" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="B12" t="s">
-        <v>55</v>
-      </c>
       <c r="E12" t="s">
-        <v>46</v>
+        <v>41</v>
       </c>
       <c r="G12">
         <v>6</v>
       </c>
       <c r="H12" t="s">
+        <v>100</v>
+      </c>
+      <c r="I12" t="s">
+        <v>45</v>
+      </c>
+      <c r="J12" t="s">
         <v>50</v>
       </c>
-      <c r="I12" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="13" spans="1:9" x14ac:dyDescent="0.25">
+    </row>
+    <row r="13" spans="1:10" x14ac:dyDescent="0.25">
       <c r="B13" t="s">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="C13" t="s">
-        <v>27</v>
+        <v>22</v>
       </c>
       <c r="D13" t="s">
-        <v>42</v>
+        <v>37</v>
       </c>
       <c r="E13" t="s">
-        <v>44</v>
+        <v>39</v>
       </c>
       <c r="F13" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="G13">
         <v>1</v>
       </c>
       <c r="H13" t="s">
+        <v>101</v>
+      </c>
+      <c r="I13" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="14" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="B14" t="s">
+        <v>46</v>
+      </c>
+      <c r="C14" t="s">
+        <v>22</v>
+      </c>
+      <c r="D14" t="s">
+        <v>52</v>
+      </c>
+      <c r="E14" t="s">
         <v>41</v>
       </c>
-    </row>
-    <row r="14" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="B14" t="s">
-        <v>51</v>
-      </c>
-      <c r="C14" t="s">
-        <v>27</v>
-      </c>
-      <c r="D14" t="s">
-        <v>58</v>
-      </c>
-      <c r="E14" t="s">
-        <v>46</v>
-      </c>
       <c r="F14" t="s">
-        <v>59</v>
+        <v>53</v>
       </c>
       <c r="G14">
         <v>1</v>
       </c>
       <c r="H14" t="s">
-        <v>74</v>
+        <v>102</v>
       </c>
       <c r="I14" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="15" spans="1:9" x14ac:dyDescent="0.25">
+        <v>66</v>
+      </c>
+      <c r="J14" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="15" spans="1:10" x14ac:dyDescent="0.25">
       <c r="B15" t="s">
-        <v>84</v>
+        <v>75</v>
       </c>
       <c r="C15" t="s">
-        <v>27</v>
+        <v>22</v>
       </c>
       <c r="D15" t="s">
-        <v>38</v>
+        <v>33</v>
       </c>
       <c r="E15" t="s">
-        <v>35</v>
+        <v>30</v>
       </c>
       <c r="F15" t="s">
-        <v>36</v>
+        <v>31</v>
       </c>
       <c r="G15">
         <v>1</v>
       </c>
       <c r="H15" t="s">
-        <v>37</v>
+        <v>103</v>
       </c>
       <c r="I15" t="s">
-        <v>69</v>
-      </c>
-    </row>
-    <row r="16" spans="1:9" x14ac:dyDescent="0.25">
+        <v>32</v>
+      </c>
+      <c r="J15" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="16" spans="1:10" x14ac:dyDescent="0.25">
       <c r="B16" t="s">
-        <v>18</v>
+        <v>13</v>
       </c>
       <c r="C16" t="s">
-        <v>27</v>
+        <v>22</v>
       </c>
       <c r="D16" t="s">
-        <v>40</v>
+        <v>35</v>
       </c>
       <c r="E16" t="s">
-        <v>39</v>
+        <v>34</v>
       </c>
       <c r="F16" t="s">
-        <v>26</v>
+        <v>21</v>
       </c>
       <c r="G16">
         <v>1</v>
       </c>
       <c r="H16" t="s">
-        <v>19</v>
+        <v>104</v>
       </c>
       <c r="I16" t="s">
-        <v>73</v>
-      </c>
-    </row>
-    <row r="17" spans="1:10" x14ac:dyDescent="0.25">
+        <v>14</v>
+      </c>
+      <c r="J16" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="17" spans="1:11" x14ac:dyDescent="0.25">
       <c r="B17" t="s">
+        <v>18</v>
+      </c>
+      <c r="C17" t="s">
+        <v>22</v>
+      </c>
+      <c r="D17" t="s">
+        <v>25</v>
+      </c>
+      <c r="E17" t="s">
         <v>23</v>
       </c>
-      <c r="C17" t="s">
-        <v>27</v>
-      </c>
-      <c r="D17" t="s">
-        <v>30</v>
-      </c>
-      <c r="E17" t="s">
-        <v>28</v>
-      </c>
       <c r="F17" t="s">
-        <v>29</v>
+        <v>24</v>
       </c>
       <c r="G17">
         <v>1</v>
       </c>
       <c r="H17" t="s">
-        <v>20</v>
+        <v>105</v>
       </c>
       <c r="I17" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="18" spans="1:10" x14ac:dyDescent="0.25">
+        <v>15</v>
+      </c>
+      <c r="J17" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="18" spans="1:11" x14ac:dyDescent="0.25">
       <c r="B18" t="s">
-        <v>24</v>
+        <v>19</v>
       </c>
       <c r="C18" t="s">
+        <v>22</v>
+      </c>
+      <c r="D18" t="s">
+        <v>28</v>
+      </c>
+      <c r="E18" t="s">
+        <v>23</v>
+      </c>
+      <c r="F18" t="s">
         <v>27</v>
-      </c>
-      <c r="D18" t="s">
-        <v>33</v>
-      </c>
-      <c r="E18" t="s">
-        <v>28</v>
-      </c>
-      <c r="F18" t="s">
-        <v>32</v>
       </c>
       <c r="G18">
         <v>2</v>
       </c>
       <c r="H18" t="s">
+        <v>106</v>
+      </c>
+      <c r="I18" t="s">
+        <v>17</v>
+      </c>
+      <c r="J18" t="s">
+        <v>26</v>
+      </c>
+      <c r="K18" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="19" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="B19" t="s">
+        <v>78</v>
+      </c>
+      <c r="C19" t="s">
         <v>22</v>
       </c>
-      <c r="I18" t="s">
-        <v>31</v>
-      </c>
-      <c r="J18" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="19" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="B19" t="s">
-        <v>87</v>
-      </c>
-      <c r="C19" t="s">
-        <v>27</v>
-      </c>
       <c r="D19" t="s">
-        <v>86</v>
+        <v>77</v>
       </c>
       <c r="E19" t="s">
-        <v>34</v>
+        <v>29</v>
       </c>
       <c r="F19" t="s">
-        <v>85</v>
+        <v>76</v>
       </c>
       <c r="G19">
         <v>1</v>
       </c>
       <c r="H19" t="s">
-        <v>88</v>
+        <v>93</v>
       </c>
       <c r="I19" t="s">
-        <v>89</v>
-      </c>
-    </row>
-    <row r="20" spans="1:10" x14ac:dyDescent="0.25">
+        <v>79</v>
+      </c>
+      <c r="J19" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="20" spans="1:11" x14ac:dyDescent="0.25">
       <c r="B20" t="s">
-        <v>11</v>
+        <v>83</v>
       </c>
       <c r="E20" t="s">
-        <v>46</v>
+        <v>41</v>
       </c>
       <c r="G20">
         <v>2</v>
       </c>
-      <c r="H20" t="s">
-        <v>91</v>
-      </c>
       <c r="I20" t="s">
-        <v>90</v>
-      </c>
-    </row>
-    <row r="22" spans="1:10" ht="18.75" x14ac:dyDescent="0.3">
+        <v>82</v>
+      </c>
+      <c r="J20" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="22" spans="1:11" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A22" s="2" t="s">
-        <v>47</v>
+        <v>42</v>
       </c>
       <c r="B22" s="2"/>
       <c r="C22" s="2"/>
@@ -1153,91 +1253,93 @@
       <c r="G22" s="2"/>
       <c r="H22" s="2"/>
       <c r="I22" s="2"/>
-    </row>
-    <row r="23" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="J22" s="2"/>
+    </row>
+    <row r="23" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A23" s="1"/>
       <c r="B23" s="1" t="s">
         <v>1</v>
       </c>
       <c r="C23" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="D23" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="D23" s="1" t="s">
+      <c r="E23" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="E23" s="1" t="s">
+      <c r="F23" s="1" t="s">
         <v>7</v>
-      </c>
-      <c r="F23" s="1" t="s">
-        <v>8</v>
       </c>
       <c r="G23" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="H23" s="1" t="s">
-        <v>9</v>
-      </c>
+      <c r="H23" s="3"/>
       <c r="I23" s="1" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="24" spans="1:10" x14ac:dyDescent="0.25">
+        <v>8</v>
+      </c>
+      <c r="J23" s="1" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="24" spans="1:11" x14ac:dyDescent="0.25">
       <c r="B24" t="s">
-        <v>71</v>
+        <v>88</v>
       </c>
       <c r="E24" t="s">
-        <v>46</v>
+        <v>41</v>
       </c>
       <c r="G24">
         <v>2</v>
       </c>
-      <c r="H24" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="25" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="I24" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="25" spans="1:11" x14ac:dyDescent="0.25">
       <c r="B25" t="s">
-        <v>53</v>
+        <v>48</v>
       </c>
       <c r="C25" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="28" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A28" s="1" t="s">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="29" spans="1:10" x14ac:dyDescent="0.25">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="27" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A27" s="1" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="28" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="B28" t="s">
+        <v>68</v>
+      </c>
+      <c r="D28" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="29" spans="1:11" x14ac:dyDescent="0.25">
       <c r="B29" t="s">
-        <v>76</v>
+        <v>69</v>
       </c>
       <c r="D29" t="s">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="30" spans="1:10" x14ac:dyDescent="0.25">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="30" spans="1:11" x14ac:dyDescent="0.25">
       <c r="B30" t="s">
-        <v>77</v>
+        <v>70</v>
       </c>
       <c r="D30" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="31" spans="1:10" x14ac:dyDescent="0.25">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="31" spans="1:11" x14ac:dyDescent="0.25">
       <c r="B31" t="s">
-        <v>78</v>
+        <v>71</v>
       </c>
       <c r="D31" t="s">
-        <v>81</v>
-      </c>
-    </row>
-    <row r="32" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="B32" t="s">
-        <v>79</v>
-      </c>
-      <c r="D32" t="s">
-        <v>83</v>
+        <v>74</v>
       </c>
     </row>
   </sheetData>
